--- a/ZELDA.xlsx
+++ b/ZELDA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\timeline-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5F9DC1-9B2C-4723-A7EE-576143E72248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FB8882-5958-4DFC-8238-2F9DE063AD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{544A5710-79AF-4C5F-8C3A-ADA1AE421E72}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="161">
   <si>
     <t>id</t>
   </si>
@@ -73,36 +73,24 @@
     <t>Adult Timeline, Child Timeline, Downfall Timeline</t>
   </si>
   <si>
-    <t>ss.jpg</t>
-  </si>
-  <si>
     <t>zd12</t>
   </si>
   <si>
     <t>The Legend of Zelda: The Minish Cap</t>
   </si>
   <si>
-    <t>tmc.jpg</t>
-  </si>
-  <si>
     <t>zd9</t>
   </si>
   <si>
     <t>The Legend of Zelda: Four Swords</t>
   </si>
   <si>
-    <t>fs.jpg</t>
-  </si>
-  <si>
     <t>zd5</t>
   </si>
   <si>
     <t>The Legend of Zelda: Ocarina of Time</t>
   </si>
   <si>
-    <t>oot.jpg</t>
-  </si>
-  <si>
     <t>zd6</t>
   </si>
   <si>
@@ -112,9 +100,6 @@
     <t>Child Timeline</t>
   </si>
   <si>
-    <t>mm.jpg</t>
-  </si>
-  <si>
     <t>zd3</t>
   </si>
   <si>
@@ -124,9 +109,6 @@
     <t>Downfall Timeline</t>
   </si>
   <si>
-    <t>alttp.jpg</t>
-  </si>
-  <si>
     <t>zd10</t>
   </si>
   <si>
@@ -139,18 +121,12 @@
     <t>The Legend of Zelda: Oracle of Seasons</t>
   </si>
   <si>
-    <t>oos.jpg</t>
-  </si>
-  <si>
     <t>zd8</t>
   </si>
   <si>
     <t>The Legend of Zelda: Oracle of Ages</t>
   </si>
   <si>
-    <t>ooa.jpg</t>
-  </si>
-  <si>
     <t>zd14</t>
   </si>
   <si>
@@ -160,90 +136,60 @@
     <t>Adult Timeline</t>
   </si>
   <si>
-    <t>ph.jpg</t>
-  </si>
-  <si>
     <t>zd13</t>
   </si>
   <si>
     <t>The Legend of Zelda: Twilight Princess</t>
   </si>
   <si>
-    <t>tp.jpg</t>
-  </si>
-  <si>
     <t>zd4</t>
   </si>
   <si>
     <t>The Legend of Zelda: Link's Awakening</t>
   </si>
   <si>
-    <t>la.jpg</t>
-  </si>
-  <si>
     <t>zd17</t>
   </si>
   <si>
     <t>The Legend of Zelda: A Link Between Worlds</t>
   </si>
   <si>
-    <t>albw.jpg</t>
-  </si>
-  <si>
     <t>zd22</t>
   </si>
   <si>
     <t>The Legend of Zelda: Echoes of Wisdom</t>
   </si>
   <si>
-    <t>eow.jpg</t>
-  </si>
-  <si>
     <t>zd18</t>
   </si>
   <si>
     <t>The Legend of Zelda: Tri Force Heroes</t>
   </si>
   <si>
-    <t>tfh.jpg</t>
-  </si>
-  <si>
     <t>zd11</t>
   </si>
   <si>
     <t>The Legend of Zelda: Four Swords Adventures</t>
   </si>
   <si>
-    <t>fsa.jpg</t>
-  </si>
-  <si>
     <t>zd15</t>
   </si>
   <si>
     <t>The Legend of Zelda: Spirit Tracks</t>
   </si>
   <si>
-    <t>st.jpg</t>
-  </si>
-  <si>
     <t>zd1</t>
   </si>
   <si>
     <t>The Legend of Zelda</t>
   </si>
   <si>
-    <t>tloz.jpg</t>
-  </si>
-  <si>
     <t>zd2</t>
   </si>
   <si>
     <t>Zelda II: The Adventure of Link</t>
   </si>
   <si>
-    <t>taol.jpg</t>
-  </si>
-  <si>
     <t>zd23</t>
   </si>
   <si>
@@ -253,114 +199,63 @@
     <t>Wild Timeline</t>
   </si>
   <si>
-    <t>aoi.jpg</t>
-  </si>
-  <si>
     <t>zd20</t>
   </si>
   <si>
     <t>Hyrule Warriors: Age of Calamity</t>
   </si>
   <si>
-    <t>aoc.jpg</t>
-  </si>
-  <si>
     <t>zd19</t>
   </si>
   <si>
     <t>The Legend of Zelda: Breath of the Wild</t>
   </si>
   <si>
-    <t>botw.jpg</t>
-  </si>
-  <si>
     <t>zd21</t>
   </si>
   <si>
     <t>The Legend of Zelda: Tears of the Kingdom</t>
   </si>
   <si>
-    <t>totk.jpg</t>
-  </si>
-  <si>
     <t>The Legend of Zelda: Link's Awakening DX</t>
   </si>
   <si>
     <t>Video Game (Remaster)</t>
   </si>
   <si>
-    <t>ladx.jpg</t>
-  </si>
-  <si>
     <t>Freshly-Picked Tingle's Rosy Rupeeland</t>
   </si>
   <si>
     <t>Video Game (Spinoff)</t>
   </si>
   <si>
-    <t>fptrr.jpg</t>
-  </si>
-  <si>
     <t>Link's Crossbow Training</t>
   </si>
   <si>
-    <t>lct.jpg</t>
-  </si>
-  <si>
     <t>The Legend of Zelda: Ocarina of Time 3D</t>
   </si>
   <si>
-    <t>oot3d.jpg</t>
-  </si>
-  <si>
     <t>The Legend of Zelda: The Wind Waker HD</t>
   </si>
   <si>
-    <t>twwhd.jpg</t>
-  </si>
-  <si>
-    <t>tww.jpg</t>
-  </si>
-  <si>
     <t>Hyrule Warriors</t>
   </si>
   <si>
-    <t>hw.jpg</t>
-  </si>
-  <si>
     <t>The Legend of Zelda: Majora's Mask 3D</t>
   </si>
   <si>
-    <t>mm3d.jpg</t>
-  </si>
-  <si>
     <t>The Legend of Zelda: Twilight Princess HD</t>
   </si>
   <si>
-    <t>tphd.jpg</t>
-  </si>
-  <si>
     <t>Hyrule Warriors Legends</t>
   </si>
   <si>
-    <t>hwl.jpg</t>
-  </si>
-  <si>
     <t>Hyrule Warriors: Definitive Edition</t>
   </si>
   <si>
-    <t>hwde.jpg</t>
-  </si>
-  <si>
-    <t>lar.jpg</t>
-  </si>
-  <si>
     <t>The Legend of Zelda: Skyward Sword HD</t>
   </si>
   <si>
-    <t>sshd.jpg</t>
-  </si>
-  <si>
     <t>The Legend of Zelda: Link's Awakening (Remake)</t>
   </si>
   <si>
@@ -398,13 +293,226 @@
   </si>
   <si>
     <t>zd35</t>
+  </si>
+  <si>
+    <t>igdb url</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co1uii.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/zelda-ii-the-adventure-of-link</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co1uje.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-a-link-to-the-past</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3vzn.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-links-awakening</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3nnt.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3nnx.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-link-s-awakening-dx</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co4o47.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-majora-s-mask</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3pah.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-oracle-of-seasons</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-ocarina-of-time</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co2tw0.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-oracle-of-ages</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co2tw1.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-four-swords</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co5w9w.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-the-wind-waker</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3ohz.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob9xf.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-four-swords-adventures</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-the-minish-cap</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3nsk.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/freshly-picked-tingles-rosy-rupeeland</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co2ymm.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-twilight-princess</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3mtv.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-phantom-hourglass</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3ocu.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/link-s-crossbow-training</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3ocw.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-spirit-tracks</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3oj6.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-ocarina-of-time-3d</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co600u.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-skyward-sword</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co5wrj.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-the-wind-waker-hd</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3ozi.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-a-link-between-worlds</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3p0j.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/hyrule-warriors</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3p0r.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-majoras-mask-3d</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob9x9.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-tri-force-heroes</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3p1a.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/hyrule-warriors-legends</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co5j9o.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-twilight-princess-hd</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3mqa.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-breath-of-the-wild</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3p2d.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/hyrule-warriors-definitive-edition</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob2j6.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-links-awakening--1</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co1qve.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/hyrule-warriors-age-of-calamity</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob22n.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-skyward-sword-hd</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob8lb.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-tears-of-the-kingdom</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co5vmg.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/the-legend-of-zelda-echoes-of-wisdom</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co8d9b.webp</t>
+  </si>
+  <si>
+    <t>https://www.igdb.com/games/hyrule-warriors-age-of-imprisonment</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob9n1.webp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -545,6 +653,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -843,7 +959,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -886,11 +1002,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -924,6 +1042,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1264,15 +1383,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D7D8C5C-82D0-4767-86A0-EC7D017C2964}">
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="46.85546875" customWidth="1"/>
     <col min="9" max="9" width="27.28515625" customWidth="1"/>
     <col min="10" max="10" width="49.140625" customWidth="1"/>
+    <col min="11" max="11" width="39.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1309,10 +1429,13 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1321,21 +1444,24 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="I2" t="s">
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="M2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1344,21 +1470,24 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="I3" t="s">
         <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="M3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1367,21 +1496,24 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
         <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="M4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1390,21 +1522,24 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1413,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s">
         <v>14</v>
@@ -1422,12 +1557,15 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1436,21 +1574,24 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="M7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1459,21 +1600,24 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
         <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="M8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1482,21 +1626,24 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I9" t="s">
         <v>14</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="M9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1505,21 +1652,24 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
         <v>14</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="M10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1528,7 +1678,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
         <v>14</v>
@@ -1537,12 +1687,15 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="M11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -1551,21 +1704,24 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I12" t="s">
         <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="K12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="M12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -1574,21 +1730,24 @@
         <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
         <v>14</v>
       </c>
       <c r="J13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -1597,7 +1756,7 @@
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
         <v>14</v>
@@ -1606,12 +1765,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="M14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -1620,21 +1782,24 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="I15" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="J15" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="M15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -1643,19 +1808,22 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I16" t="s">
         <v>14</v>
       </c>
       <c r="J16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="M16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1666,21 +1834,24 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I17" t="s">
         <v>14</v>
       </c>
       <c r="J17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="K17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="M17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -1689,21 +1860,24 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="I18" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="J18" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="M18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -1712,21 +1886,24 @@
         <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="I19" t="s">
         <v>14</v>
       </c>
       <c r="J19" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="K19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="M19" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -1735,21 +1912,24 @@
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="I20" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="J20" t="s">
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="M20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -1767,12 +1947,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="M21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -1781,21 +1964,24 @@
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="I22" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="J22" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="K22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="M22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -1804,21 +1990,24 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I23" t="s">
         <v>14</v>
       </c>
       <c r="J23" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="M23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -1827,7 +2016,7 @@
         <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="I24" t="s">
         <v>14</v>
@@ -1836,12 +2025,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="M24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -1850,21 +2042,24 @@
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="J25" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="M25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -1873,21 +2068,24 @@
         <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="I26" t="s">
         <v>14</v>
       </c>
       <c r="J26" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="M26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -1896,21 +2094,24 @@
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="J27" t="s">
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="M27" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -1919,21 +2120,24 @@
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="J28" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+      <c r="M28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -1942,21 +2146,24 @@
         <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="I29" t="s">
         <v>14</v>
       </c>
       <c r="J29" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="K29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="M29" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="B30">
         <v>29</v>
@@ -1965,21 +2172,24 @@
         <v>31</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="M30" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="B31">
         <v>30</v>
@@ -1988,21 +2198,24 @@
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="J31" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K31" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="M31" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="B32">
         <v>31</v>
@@ -2011,21 +2224,24 @@
         <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="I32" t="s">
         <v>14</v>
       </c>
       <c r="J32" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="K32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="M32" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="B33">
         <v>32</v>
@@ -2034,21 +2250,24 @@
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="I33" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="J33" t="s">
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="M33" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="B34">
         <v>33</v>
@@ -2057,21 +2276,24 @@
         <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
         <v>14</v>
       </c>
       <c r="J34" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="K34" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="M34" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="B35">
         <v>34</v>
@@ -2080,21 +2302,24 @@
         <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="I35" t="s">
         <v>14</v>
       </c>
       <c r="J35" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="M35" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="B36">
         <v>35</v>
@@ -2103,16 +2328,19 @@
         <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="I36" t="s">
         <v>14</v>
       </c>
       <c r="J36" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="K36" t="s">
-        <v>76</v>
+        <v>160</v>
+      </c>
+      <c r="M36" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2122,6 +2350,10 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="M6" r:id="rId1" xr:uid="{9D13AB1B-17E5-47B8-8BB4-A42EF0F05C18}"/>
+    <hyperlink ref="M13" r:id="rId2" xr:uid="{5D408525-0FF4-4DD4-8542-509FE990F36A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ZELDA.xlsx
+++ b/ZELDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\timeline-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FB8882-5958-4DFC-8238-2F9DE063AD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A9B4F1-A1D1-45FE-A3FB-2265811439FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{544A5710-79AF-4C5F-8C3A-ADA1AE421E72}"/>
   </bookViews>
@@ -301,211 +301,211 @@
     <t>https://www.igdb.com/games/the-legend-of-zelda</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co1uii.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/zelda-ii-the-adventure-of-link</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co1uje.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-a-link-to-the-past</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3vzn.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-links-awakening</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3nnt.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3nnx.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-link-s-awakening-dx</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co4o47.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-majora-s-mask</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3pah.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-oracle-of-seasons</t>
   </si>
   <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-ocarina-of-time</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co2tw0.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-oracle-of-ages</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co2tw1.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-four-swords</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co5w9w.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-the-wind-waker</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3ohz.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob9xf.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-four-swords-adventures</t>
   </si>
   <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-the-minish-cap</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3nsk.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/freshly-picked-tingles-rosy-rupeeland</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co2ymm.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-twilight-princess</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3mtv.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-phantom-hourglass</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3ocu.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/link-s-crossbow-training</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3ocw.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-spirit-tracks</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3oj6.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-ocarina-of-time-3d</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co600u.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-skyward-sword</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co5wrj.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-the-wind-waker-hd</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3ozi.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-a-link-between-worlds</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3p0j.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/hyrule-warriors</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3p0r.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-majoras-mask-3d</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob9x9.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-tri-force-heroes</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3p1a.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/hyrule-warriors-legends</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co5j9o.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-twilight-princess-hd</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3mqa.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-breath-of-the-wild</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co3p2d.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/hyrule-warriors-definitive-edition</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob2j6.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-links-awakening--1</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co1qve.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/hyrule-warriors-age-of-calamity</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob22n.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-skyward-sword-hd</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob8lb.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-tears-of-the-kingdom</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co5vmg.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/the-legend-of-zelda-echoes-of-wisdom</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/co8d9b.webp</t>
-  </si>
-  <si>
     <t>https://www.igdb.com/games/hyrule-warriors-age-of-imprisonment</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big/cob9n1.webp</t>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co1uii.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co1uje.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3vzn.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3nnt.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3nnx.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co4o47.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3pah.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co2tw0.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co2tw1.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co5w9w.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3ohz.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob9xf.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3nsk.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co2ymm.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3mtv.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3ocu.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3ocw.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3oj6.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co600u.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co5wrj.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3ozi.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3p0j.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3p0r.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob9x9.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3p1a.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co5j9o.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3mqa.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3p2d.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob2j6.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co1qve.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob22n.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob8lb.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co5vmg.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co8d9b.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob9n1.webp</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1389,7 @@
     <col min="4" max="4" width="46.85546875" customWidth="1"/>
     <col min="9" max="9" width="27.28515625" customWidth="1"/>
     <col min="10" max="10" width="49.140625" customWidth="1"/>
-    <col min="11" max="11" width="39.7109375" customWidth="1"/>
+    <col min="11" max="11" width="72.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1453,7 +1453,7 @@
         <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="M2" t="s">
         <v>91</v>
@@ -1479,10 +1479,10 @@
         <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="M3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -1505,10 +1505,10 @@
         <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="M4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1531,10 +1531,10 @@
         <v>27</v>
       </c>
       <c r="K5" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="M5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -1557,10 +1557,10 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -1583,10 +1583,10 @@
         <v>27</v>
       </c>
       <c r="K7" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="M7" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -1609,10 +1609,10 @@
         <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1635,10 +1635,10 @@
         <v>27</v>
       </c>
       <c r="K9" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -1661,10 +1661,10 @@
         <v>27</v>
       </c>
       <c r="K10" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="M10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -1687,10 +1687,10 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="M11" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -1713,10 +1713,10 @@
         <v>36</v>
       </c>
       <c r="K12" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="M12" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -1739,10 +1739,10 @@
         <v>24</v>
       </c>
       <c r="K13" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -1765,10 +1765,10 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="M14" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -1791,10 +1791,10 @@
         <v>24</v>
       </c>
       <c r="K15" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="M15" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -1817,10 +1817,10 @@
         <v>24</v>
       </c>
       <c r="K16" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="M16" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -1843,10 +1843,10 @@
         <v>36</v>
       </c>
       <c r="K17" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="M17" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -1869,10 +1869,10 @@
         <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="M18" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -1895,10 +1895,10 @@
         <v>36</v>
       </c>
       <c r="K19" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="M19" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -1921,10 +1921,10 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -1947,10 +1947,10 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -1973,10 +1973,10 @@
         <v>36</v>
       </c>
       <c r="K22" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="M22" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -1999,10 +1999,10 @@
         <v>27</v>
       </c>
       <c r="K23" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="M23" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -2025,10 +2025,10 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="M24" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -2051,10 +2051,10 @@
         <v>24</v>
       </c>
       <c r="K25" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="M25" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -2077,10 +2077,10 @@
         <v>27</v>
       </c>
       <c r="K26" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="M26" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -2103,10 +2103,10 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="M27" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -2129,10 +2129,10 @@
         <v>24</v>
       </c>
       <c r="K28" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="M28" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -2155,10 +2155,10 @@
         <v>57</v>
       </c>
       <c r="K29" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="M29" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -2181,10 +2181,10 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="M30" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -2207,10 +2207,10 @@
         <v>27</v>
       </c>
       <c r="K31" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M31" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -2233,10 +2233,10 @@
         <v>57</v>
       </c>
       <c r="K32" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M32" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -2259,10 +2259,10 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M33" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -2285,10 +2285,10 @@
         <v>57</v>
       </c>
       <c r="K34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M34" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -2311,10 +2311,10 @@
         <v>27</v>
       </c>
       <c r="K35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M35" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -2340,7 +2340,7 @@
         <v>160</v>
       </c>
       <c r="M36" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/ZELDA.xlsx
+++ b/ZELDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\timeline-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A9B4F1-A1D1-45FE-A3FB-2265811439FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1358A9F-6CAA-4001-82FD-6909EF5CB4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{544A5710-79AF-4C5F-8C3A-ADA1AE421E72}"/>
   </bookViews>
@@ -403,109 +403,109 @@
     <t>https://www.igdb.com/games/hyrule-warriors-age-of-imprisonment</t>
   </si>
   <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co1uii.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co1uje.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3vzn.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3nnt.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3nnx.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co4o47.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3pah.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co2tw0.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co2tw1.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co5w9w.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3ohz.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob9xf.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3nsk.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co2ymm.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3mtv.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3ocu.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3ocw.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3oj6.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co600u.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co5wrj.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3ozi.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3p0j.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3p0r.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob9x9.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3p1a.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co5j9o.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3mqa.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co3p2d.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob2j6.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co1qve.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob22n.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob8lb.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co5vmg.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/co8d9b.webp</t>
-  </si>
-  <si>
-    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_x2/cob9n1.webp</t>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co1uii.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co1uje.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3vzn.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3nnt.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3nnx.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co4o47.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3pah.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co2tw0.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co2tw1.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co5w9w.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3ohz.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/cob9xf.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3nsk.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co2ymm.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3mtv.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3ocu.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3ocw.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3oj6.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co600u.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co5wrj.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3ozi.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3p0j.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3p0r.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/cob9x9.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3p1a.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co5j9o.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3mqa.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co3p2d.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/cob2j6.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co1qve.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/cob22n.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/cob8lb.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co5vmg.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/co8d9b.webp</t>
+  </si>
+  <si>
+    <t>https://images.igdb.com/igdb/image/upload/t_cover_big_2x/cob9n1.webp</t>
   </si>
 </sst>
 </file>
